--- a/Data/EXCEL/Transfer/salemon/202206/6870-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6870-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DED1A6E-14A4-4AE9-A179-6E9A76EF7E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD73A541-0CC0-4566-AB7A-ED48645E5712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6870-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1218,21 +1218,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.125" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="10.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="15" width="10.5" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,272 +1385,272 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>157.5</v>
+        <v>163.5</v>
       </c>
       <c r="C5" s="7">
-        <v>163.5</v>
+        <v>167</v>
       </c>
       <c r="D5" s="7">
-        <v>167</v>
+        <v>168.5</v>
       </c>
       <c r="E5" s="7">
-        <v>145</v>
+        <v>155.5</v>
       </c>
       <c r="F5" s="8">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="G5" s="8">
-        <v>3.81</v>
+        <v>2.14</v>
       </c>
       <c r="H5" s="9">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="I5" s="8">
-        <v>9.39</v>
-      </c>
-      <c r="J5" s="8">
-        <v>12.4</v>
+        <v>0.313</v>
+      </c>
+      <c r="I5" s="10">
+        <v>-6.57</v>
+      </c>
+      <c r="J5" s="10">
+        <v>-22.9</v>
       </c>
       <c r="K5" s="9">
-        <v>1.76</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L5" s="8">
-        <v>28.4</v>
+        <v>16.7</v>
       </c>
       <c r="M5" s="9">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="N5" s="8">
-        <v>9.39</v>
-      </c>
-      <c r="O5" s="8">
-        <v>12.4</v>
+        <v>0.313</v>
+      </c>
+      <c r="N5" s="10">
+        <v>-6.57</v>
+      </c>
+      <c r="O5" s="10">
+        <v>-22.9</v>
       </c>
       <c r="P5" s="9">
-        <v>1.76</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="Q5" s="8">
-        <v>28.4</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>162</v>
+        <v>157.5</v>
       </c>
       <c r="C6" s="7">
-        <v>157.5</v>
+        <v>163.5</v>
       </c>
       <c r="D6" s="7">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E6" s="7">
-        <v>149</v>
-      </c>
-      <c r="F6" s="10">
-        <v>-4.5</v>
-      </c>
-      <c r="G6" s="10">
-        <v>-2.78</v>
+        <v>145</v>
+      </c>
+      <c r="F6" s="8">
+        <v>6</v>
+      </c>
+      <c r="G6" s="8">
+        <v>3.81</v>
       </c>
       <c r="H6" s="9">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="I6" s="10">
-        <v>-21.4</v>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I6" s="8">
+        <v>9.39</v>
       </c>
       <c r="J6" s="8">
-        <v>9.52</v>
+        <v>12.4</v>
       </c>
       <c r="K6" s="9">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="L6" s="8">
-        <v>32.799999999999997</v>
+        <v>28.4</v>
       </c>
       <c r="M6" s="9">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="N6" s="10">
-        <v>-21.4</v>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="N6" s="8">
+        <v>9.39</v>
       </c>
       <c r="O6" s="8">
-        <v>9.52</v>
+        <v>12.4</v>
       </c>
       <c r="P6" s="9">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" s="8">
-        <v>32.799999999999997</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="C7" s="7">
-        <v>162</v>
+        <v>157.5</v>
       </c>
       <c r="D7" s="7">
-        <v>212.5</v>
+        <v>170</v>
       </c>
       <c r="E7" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F7" s="10">
-        <v>-20</v>
+        <v>-4.5</v>
       </c>
       <c r="G7" s="10">
-        <v>-10.99</v>
+        <v>-2.78</v>
       </c>
       <c r="H7" s="9">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="I7" s="8">
-        <v>10.7</v>
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="I7" s="10">
+        <v>-21.4</v>
       </c>
       <c r="J7" s="8">
-        <v>67.099999999999994</v>
+        <v>9.52</v>
       </c>
       <c r="K7" s="9">
-        <v>1.1200000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="L7" s="8">
-        <v>41</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="M7" s="9">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="N7" s="8">
-        <v>10.7</v>
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N7" s="10">
+        <v>-21.4</v>
       </c>
       <c r="O7" s="8">
-        <v>67.099999999999994</v>
+        <v>9.52</v>
       </c>
       <c r="P7" s="9">
-        <v>1.1200000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="Q7" s="8">
-        <v>41</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="C8" s="7">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="D8" s="7">
-        <v>264.5</v>
+        <v>212.5</v>
       </c>
       <c r="E8" s="7">
-        <v>129</v>
-      </c>
-      <c r="F8" s="8">
-        <v>32</v>
-      </c>
-      <c r="G8" s="8">
-        <v>21.33</v>
+        <v>152</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-20</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-10.99</v>
       </c>
       <c r="H8" s="9">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="I8" s="10">
-        <v>-7.41</v>
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="I8" s="8">
+        <v>10.7</v>
       </c>
       <c r="J8" s="8">
-        <v>52.2</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="K8" s="9">
-        <v>0.73099999999999998</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="L8" s="8">
-        <v>30.2</v>
+        <v>41</v>
       </c>
       <c r="M8" s="9">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="N8" s="10">
-        <v>-7.41</v>
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="N8" s="8">
+        <v>10.7</v>
       </c>
       <c r="O8" s="8">
-        <v>52.2</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="P8" s="9">
-        <v>0.73099999999999998</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="Q8" s="8">
-        <v>30.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>17</v>
+        <v>44593</v>
+      </c>
+      <c r="B9" s="7">
+        <v>150</v>
+      </c>
+      <c r="C9" s="7">
+        <v>182</v>
+      </c>
+      <c r="D9" s="7">
+        <v>264.5</v>
+      </c>
+      <c r="E9" s="7">
+        <v>129</v>
+      </c>
+      <c r="F9" s="8">
+        <v>32</v>
+      </c>
+      <c r="G9" s="8">
+        <v>21.33</v>
       </c>
       <c r="H9" s="9">
-        <v>0.38</v>
-      </c>
-      <c r="I9" s="8">
-        <v>13.7</v>
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="I9" s="10">
+        <v>-7.41</v>
       </c>
       <c r="J9" s="8">
-        <v>14.8</v>
+        <v>52.2</v>
       </c>
       <c r="K9" s="9">
-        <v>0.38</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="L9" s="8">
-        <v>14.8</v>
+        <v>30.2</v>
       </c>
       <c r="M9" s="9">
-        <v>0.38</v>
-      </c>
-      <c r="N9" s="8">
-        <v>13.7</v>
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="N9" s="10">
+        <v>-7.41</v>
       </c>
       <c r="O9" s="8">
-        <v>14.8</v>
+        <v>52.2</v>
       </c>
       <c r="P9" s="9">
-        <v>0.38</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="Q9" s="8">
-        <v>14.8</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>17</v>
@@ -1671,86 +1671,139 @@
         <v>17</v>
       </c>
       <c r="H10" s="9">
-        <v>0.33400000000000002</v>
-      </c>
-      <c r="I10" s="10">
-        <v>-3.15</v>
-      </c>
-      <c r="J10" s="10">
-        <v>-13</v>
+        <v>0.38</v>
+      </c>
+      <c r="I10" s="8">
+        <v>13.7</v>
+      </c>
+      <c r="J10" s="8">
+        <v>14.8</v>
       </c>
       <c r="K10" s="9">
-        <v>3.72</v>
+        <v>0.38</v>
       </c>
       <c r="L10" s="8">
-        <v>23.9</v>
+        <v>14.8</v>
       </c>
       <c r="M10" s="9">
-        <v>0.33400000000000002</v>
-      </c>
-      <c r="N10" s="10">
-        <v>-3.15</v>
-      </c>
-      <c r="O10" s="10">
-        <v>-13</v>
+        <v>0.38</v>
+      </c>
+      <c r="N10" s="8">
+        <v>13.7</v>
+      </c>
+      <c r="O10" s="8">
+        <v>14.8</v>
       </c>
       <c r="P10" s="9">
-        <v>3.72</v>
+        <v>0.38</v>
       </c>
       <c r="Q10" s="8">
-        <v>23.9</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
+        <v>44531</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-3.15</v>
+      </c>
+      <c r="J11" s="10">
+        <v>-13</v>
+      </c>
+      <c r="K11" s="9">
+        <v>3.72</v>
+      </c>
+      <c r="L11" s="8">
+        <v>23.9</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-3.15</v>
+      </c>
+      <c r="O11" s="10">
+        <v>-13</v>
+      </c>
+      <c r="P11" s="9">
+        <v>3.72</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>44501</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="9">
+      <c r="B12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="9">
         <v>0.34499999999999997</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="10">
+      <c r="I12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="10">
         <v>-24.5</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K12" s="9">
         <v>3.38</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L12" s="8">
         <v>29.3</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M12" s="9">
         <v>0.34499999999999997</v>
       </c>
-      <c r="N11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O11" s="10">
+      <c r="N12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O12" s="10">
         <v>-24.5</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P12" s="9">
         <v>3.38</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q12" s="8">
         <v>29.3</v>
       </c>
     </row>
